--- a/assets/report-template.xlsx
+++ b/assets/report-template.xlsx
@@ -2,28 +2,30 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$O$4</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode=";;;"/>
+  </numFmts>
+  <fonts count="24">
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -32,8 +34,170 @@
       <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="36">
     <fill>
       <patternFill/>
     </fill>
@@ -46,8 +210,206 @@
         <bgColor rgb="FFFFD700"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5E9"/>
+        <bgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -70,20 +432,571 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="50">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="49"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -169,6 +1082,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="1"/>
         <axPos val="l"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -180,6 +1094,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="1"/>
         <axPos val="l"/>
         <majorGridlines/>
         <majorTickMark val="none"/>
@@ -197,9 +1112,9 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>14</col>
       <colOff>0</colOff>
-      <row>1</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="3513455" cy="1031240"/>
@@ -263,72 +1178,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -384,7 +1241,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -393,13 +1250,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -433,17 +1290,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -499,7 +1345,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -509,105 +1354,502 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:V4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="32.8571428571429" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="52.9333333333333" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" style="1" min="1" max="1"/>
+    <col width="10" customWidth="1" style="1" min="2" max="2"/>
+    <col width="28" customWidth="1" style="1" min="3" max="3"/>
+    <col width="24" customWidth="1" style="1" min="4" max="4"/>
+    <col width="32.8571428571429" customWidth="1" style="1" min="5" max="5"/>
+    <col width="10" customWidth="1" style="1" min="6" max="7"/>
+    <col width="10" customWidth="1" style="1" min="7" max="7"/>
+    <col width="14" customWidth="1" style="1" min="8" max="10"/>
+    <col width="14" customWidth="1" style="1" min="9" max="9"/>
+    <col width="14" customWidth="1" style="1" min="10" max="10"/>
+    <col width="10" customWidth="1" style="1" min="11" max="11"/>
+    <col width="13" customWidth="1" style="1" min="12" max="12"/>
+    <col width="13" customWidth="1" style="1" min="13" max="13"/>
+    <col hidden="1" width="13" customWidth="1" style="1" min="14" max="14"/>
+    <col width="52.9333333333333" customWidth="1" style="1" min="15" max="15"/>
+    <col hidden="1" width="16.4285714285714" customWidth="1" style="1" min="16" max="16"/>
+    <col hidden="1" width="13" customWidth="1" style="1" min="17" max="21"/>
+    <col hidden="1" width="13" customWidth="1" style="1" min="18" max="18"/>
+    <col hidden="1" width="13" customWidth="1" style="1" min="19" max="19"/>
+    <col hidden="1" width="13" customWidth="1" style="1" min="20" max="20"/>
+    <col hidden="1" width="13" customWidth="1" style="1" min="21" max="21"/>
+    <col hidden="1" width="18" customWidth="1" style="1" min="22" max="22"/>
+    <col width="10.7142857142857" customWidth="1" style="1" min="23" max="23"/>
+    <col width="13.7142857142857" customWidth="1" style="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" style="1" min="26" max="32"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1" s="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>排名</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>近7天重点选品</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>来源</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>品名关键词</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>中文名称</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>价格(USD)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>商品评分</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>评论数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>GMV</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>7天GMV</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>7天销量</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>关联视频</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>关联达人</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>EchoTik详情链接</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>诊断</t>
         </is>
       </c>
+      <c r="P1" s="0" t="n"/>
+      <c r="Q1" s="0" t="n"/>
+      <c r="R1" s="0" t="n"/>
+      <c r="S1" s="0" t="n"/>
+      <c r="T1" s="0" t="n"/>
+      <c r="U1" s="0" t="n"/>
+      <c r="V1" s="0" t="n"/>
     </row>
+    <row r="2" ht="78" customHeight="1" s="1">
+      <c r="A2" s="3" t="n"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="78" customHeight="1" s="1">
+      <c r="A3" s="6" t="n"/>
+      <c r="B3" s="6" t="n"/>
+      <c r="C3" s="7" t="n"/>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="8" t="n"/>
+      <c r="F3" s="6" t="n"/>
+      <c r="G3" s="6" t="n"/>
+      <c r="H3" s="6" t="n"/>
+      <c r="I3" s="6" t="n"/>
+      <c r="J3" s="6" t="n"/>
+      <c r="K3" s="6" t="n"/>
+      <c r="L3" s="6" t="n"/>
+      <c r="M3" s="6" t="n"/>
+      <c r="N3" s="15" t="n"/>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="0" t="n"/>
+      <c r="Q3" s="0" t="n"/>
+      <c r="R3" s="0" t="n"/>
+      <c r="S3" s="0" t="n"/>
+      <c r="T3" s="0" t="n"/>
+      <c r="U3" s="0" t="n"/>
+      <c r="V3" s="0" t="n"/>
+    </row>
+    <row r="4" ht="78" customHeight="1" s="1">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="12" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="16" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="0" t="n"/>
+      <c r="Q4" s="0" t="n"/>
+      <c r="R4" s="0" t="n"/>
+      <c r="S4" s="0" t="n"/>
+      <c r="T4" s="0" t="n"/>
+      <c r="U4" s="0" t="n"/>
+      <c r="V4" s="0" t="n"/>
+    </row>
+    <row r="5" ht="78" customHeight="1" s="1"/>
+    <row r="6" ht="78" customHeight="1" s="1"/>
+    <row r="7" ht="78" customHeight="1" s="1"/>
+    <row r="8" ht="78" customHeight="1" s="1"/>
+    <row r="9" ht="78" customHeight="1" s="1"/>
+    <row r="10" ht="78" customHeight="1" s="1"/>
+    <row r="11" ht="78" customHeight="1" s="1"/>
+    <row r="12" ht="78" customHeight="1" s="1"/>
+    <row r="13" ht="78" customHeight="1" s="1"/>
+    <row r="14" ht="78" customHeight="1" s="1"/>
+    <row r="15" ht="78" customHeight="1" s="1"/>
+    <row r="16" ht="78" customHeight="1" s="1"/>
+    <row r="17" ht="78" customHeight="1" s="1"/>
+    <row r="18" ht="78" customHeight="1" s="1"/>
+    <row r="19" ht="78" customHeight="1" s="1"/>
+    <row r="20" ht="78" customHeight="1" s="1"/>
+    <row r="21" ht="78" customHeight="1" s="1"/>
+    <row r="22" ht="78" customHeight="1" s="1"/>
+    <row r="23" ht="78" customHeight="1" s="1"/>
+    <row r="24" ht="78" customHeight="1" s="1"/>
+    <row r="25" ht="78" customHeight="1" s="1"/>
+    <row r="26" ht="78" customHeight="1" s="1"/>
+    <row r="27" ht="78" customHeight="1" s="1"/>
+    <row r="28" ht="78" customHeight="1" s="1"/>
+    <row r="29" ht="78" customHeight="1" s="1"/>
+    <row r="30" ht="78" customHeight="1" s="1"/>
+    <row r="31" ht="78" customHeight="1" s="1"/>
+    <row r="32" ht="78" customHeight="1" s="1"/>
+    <row r="33" ht="78" customHeight="1" s="1"/>
+    <row r="34" ht="78" customHeight="1" s="1"/>
+    <row r="35" ht="78" customHeight="1" s="1"/>
+    <row r="36" ht="78" customHeight="1" s="1"/>
+    <row r="37" ht="78" customHeight="1" s="1"/>
+    <row r="38" ht="78" customHeight="1" s="1"/>
+    <row r="39" ht="78" customHeight="1" s="1"/>
+    <row r="40" ht="78" customHeight="1" s="1"/>
+    <row r="41" ht="78" customHeight="1" s="1"/>
+    <row r="42" ht="78" customHeight="1" s="1"/>
+    <row r="43" ht="78" customHeight="1" s="1"/>
+    <row r="44" ht="78" customHeight="1" s="1"/>
+    <row r="45" ht="78" customHeight="1" s="1"/>
+    <row r="46" ht="78" customHeight="1" s="1"/>
+    <row r="47" ht="78" customHeight="1" s="1"/>
+    <row r="48" ht="78" customHeight="1" s="1"/>
+    <row r="49" ht="78" customHeight="1" s="1"/>
+    <row r="50" ht="78" customHeight="1" s="1"/>
+    <row r="51" ht="78" customHeight="1" s="1"/>
+    <row r="52" ht="78" customHeight="1" s="1"/>
+    <row r="53" ht="78" customHeight="1" s="1"/>
+    <row r="54" ht="78" customHeight="1" s="1"/>
+    <row r="55" ht="78" customHeight="1" s="1"/>
+    <row r="56" ht="78" customHeight="1" s="1"/>
+    <row r="57" ht="78" customHeight="1" s="1"/>
+    <row r="58" ht="78" customHeight="1" s="1"/>
+    <row r="59" ht="78" customHeight="1" s="1"/>
+    <row r="60" ht="78" customHeight="1" s="1"/>
+    <row r="61" ht="78" customHeight="1" s="1"/>
+    <row r="62" ht="78" customHeight="1" s="1"/>
+    <row r="63" ht="78" customHeight="1" s="1"/>
+    <row r="64" ht="78" customHeight="1" s="1"/>
+    <row r="65" ht="78" customHeight="1" s="1"/>
+    <row r="66" ht="78" customHeight="1" s="1"/>
+    <row r="67" ht="78" customHeight="1" s="1"/>
+    <row r="68" ht="78" customHeight="1" s="1"/>
+    <row r="69" ht="78" customHeight="1" s="1"/>
+    <row r="70" ht="78" customHeight="1" s="1"/>
+    <row r="71" ht="78" customHeight="1" s="1"/>
+    <row r="72" ht="78" customHeight="1" s="1"/>
+    <row r="73" ht="78" customHeight="1" s="1"/>
+    <row r="74" ht="78" customHeight="1" s="1"/>
+    <row r="75" ht="78" customHeight="1" s="1"/>
+    <row r="76" ht="78" customHeight="1" s="1"/>
+    <row r="77" ht="78" customHeight="1" s="1"/>
+    <row r="78" ht="78" customHeight="1" s="1"/>
+    <row r="79" ht="78" customHeight="1" s="1"/>
+    <row r="80" ht="78" customHeight="1" s="1"/>
+    <row r="81" ht="78" customHeight="1" s="1"/>
+    <row r="82" ht="78" customHeight="1" s="1"/>
+    <row r="83" ht="78" customHeight="1" s="1"/>
+    <row r="84" ht="78" customHeight="1" s="1"/>
+    <row r="85" ht="78" customHeight="1" s="1"/>
+    <row r="86" ht="78" customHeight="1" s="1"/>
+    <row r="87" ht="78" customHeight="1" s="1"/>
+    <row r="88" ht="78" customHeight="1" s="1"/>
+    <row r="89" ht="78" customHeight="1" s="1"/>
+    <row r="90" ht="78" customHeight="1" s="1"/>
+    <row r="91" ht="78" customHeight="1" s="1"/>
+    <row r="92" ht="78" customHeight="1" s="1"/>
+    <row r="93" ht="78" customHeight="1" s="1"/>
+    <row r="94" ht="78" customHeight="1" s="1"/>
+    <row r="95" ht="78" customHeight="1" s="1"/>
+    <row r="96" ht="78" customHeight="1" s="1"/>
+    <row r="97" ht="78" customHeight="1" s="1"/>
+    <row r="98" ht="78" customHeight="1" s="1"/>
+    <row r="99" ht="78" customHeight="1" s="1"/>
+    <row r="100" ht="78" customHeight="1" s="1"/>
+    <row r="101" ht="78" customHeight="1" s="1"/>
+    <row r="102" ht="78" customHeight="1" s="1"/>
+    <row r="103" ht="78" customHeight="1" s="1"/>
+    <row r="104" ht="78" customHeight="1" s="1"/>
+    <row r="105" ht="78" customHeight="1" s="1"/>
+    <row r="106" ht="78" customHeight="1" s="1"/>
+    <row r="107" ht="78" customHeight="1" s="1"/>
+    <row r="108" ht="78" customHeight="1" s="1"/>
+    <row r="109" ht="78" customHeight="1" s="1"/>
+    <row r="110" ht="78" customHeight="1" s="1"/>
+    <row r="111" ht="78" customHeight="1" s="1"/>
+    <row r="112" ht="78" customHeight="1" s="1"/>
+    <row r="113" ht="78" customHeight="1" s="1"/>
+    <row r="114" ht="78" customHeight="1" s="1"/>
+    <row r="115" ht="78" customHeight="1" s="1"/>
+    <row r="116" ht="78" customHeight="1" s="1"/>
+    <row r="117" ht="78" customHeight="1" s="1"/>
+    <row r="118" ht="78" customHeight="1" s="1"/>
+    <row r="119" ht="78" customHeight="1" s="1"/>
+    <row r="120" ht="78" customHeight="1" s="1"/>
+    <row r="121" ht="78" customHeight="1" s="1"/>
+    <row r="122" ht="78" customHeight="1" s="1"/>
+    <row r="123" ht="78" customHeight="1" s="1"/>
+    <row r="124" ht="78" customHeight="1" s="1"/>
+    <row r="125" ht="78" customHeight="1" s="1"/>
+    <row r="126" ht="78" customHeight="1" s="1"/>
+    <row r="127" ht="78" customHeight="1" s="1"/>
+    <row r="128" ht="78" customHeight="1" s="1"/>
+    <row r="129" ht="78" customHeight="1" s="1"/>
+    <row r="130" ht="78" customHeight="1" s="1"/>
+    <row r="131" ht="78" customHeight="1" s="1"/>
+    <row r="132" ht="78" customHeight="1" s="1"/>
+    <row r="133" ht="78" customHeight="1" s="1"/>
+    <row r="134" ht="78" customHeight="1" s="1"/>
+    <row r="135" ht="78" customHeight="1" s="1"/>
+    <row r="136" ht="78" customHeight="1" s="1"/>
+    <row r="137" ht="78" customHeight="1" s="1"/>
+    <row r="138" ht="78" customHeight="1" s="1"/>
+    <row r="139" ht="78" customHeight="1" s="1"/>
+    <row r="140" ht="78" customHeight="1" s="1"/>
+    <row r="141" ht="78" customHeight="1" s="1"/>
+    <row r="142" ht="78" customHeight="1" s="1"/>
+    <row r="143" ht="78" customHeight="1" s="1"/>
+    <row r="144" ht="78" customHeight="1" s="1"/>
+    <row r="145" ht="78" customHeight="1" s="1"/>
+    <row r="146" ht="78" customHeight="1" s="1"/>
+    <row r="147" ht="78" customHeight="1" s="1"/>
+    <row r="148" ht="78" customHeight="1" s="1"/>
+    <row r="149" ht="78" customHeight="1" s="1"/>
+    <row r="150" ht="78" customHeight="1" s="1"/>
+    <row r="151" ht="78" customHeight="1" s="1"/>
+    <row r="152" ht="78" customHeight="1" s="1"/>
+    <row r="153" ht="78" customHeight="1" s="1"/>
+    <row r="154" ht="78" customHeight="1" s="1"/>
+    <row r="155" ht="78" customHeight="1" s="1"/>
+    <row r="156" ht="78" customHeight="1" s="1"/>
+    <row r="157" ht="78" customHeight="1" s="1"/>
+    <row r="158" ht="78" customHeight="1" s="1"/>
+    <row r="159" ht="78" customHeight="1" s="1"/>
+    <row r="160" ht="78" customHeight="1" s="1"/>
+    <row r="161" ht="78" customHeight="1" s="1"/>
+    <row r="162" ht="78" customHeight="1" s="1"/>
+    <row r="163" ht="78" customHeight="1" s="1"/>
+    <row r="164" ht="78" customHeight="1" s="1"/>
+    <row r="165" ht="78" customHeight="1" s="1"/>
+    <row r="166" ht="78" customHeight="1" s="1"/>
+    <row r="167" ht="78" customHeight="1" s="1"/>
+    <row r="168" ht="78" customHeight="1" s="1"/>
+    <row r="169" ht="78" customHeight="1" s="1"/>
+    <row r="170" ht="78" customHeight="1" s="1"/>
+    <row r="171" ht="78" customHeight="1" s="1"/>
+    <row r="172" ht="78" customHeight="1" s="1"/>
+    <row r="173" ht="78" customHeight="1" s="1"/>
+    <row r="174" ht="78" customHeight="1" s="1"/>
+    <row r="175" ht="78" customHeight="1" s="1"/>
+    <row r="176" ht="78" customHeight="1" s="1"/>
+    <row r="177" ht="78" customHeight="1" s="1"/>
+    <row r="178" ht="78" customHeight="1" s="1"/>
+    <row r="179" ht="78" customHeight="1" s="1"/>
+    <row r="180" ht="78" customHeight="1" s="1"/>
+    <row r="181" ht="78" customHeight="1" s="1"/>
+    <row r="182" ht="78" customHeight="1" s="1"/>
+    <row r="183" ht="78" customHeight="1" s="1"/>
+    <row r="184" ht="78" customHeight="1" s="1"/>
+    <row r="185" ht="78" customHeight="1" s="1"/>
+    <row r="186" ht="78" customHeight="1" s="1"/>
+    <row r="187" ht="78" customHeight="1" s="1"/>
+    <row r="188" ht="78" customHeight="1" s="1"/>
+    <row r="189" ht="78" customHeight="1" s="1"/>
+    <row r="190" ht="78" customHeight="1" s="1"/>
+    <row r="191" ht="78" customHeight="1" s="1"/>
+    <row r="192" ht="78" customHeight="1" s="1"/>
+    <row r="193" ht="78" customHeight="1" s="1"/>
+    <row r="194" ht="78" customHeight="1" s="1"/>
+    <row r="195" ht="78" customHeight="1" s="1"/>
+    <row r="196" ht="78" customHeight="1" s="1"/>
+    <row r="197" ht="78" customHeight="1" s="1"/>
+    <row r="198" ht="78" customHeight="1" s="1"/>
+    <row r="199" ht="78" customHeight="1" s="1"/>
+    <row r="200" ht="78" customHeight="1" s="1"/>
+    <row r="201" ht="78" customHeight="1" s="1"/>
+    <row r="202" ht="78" customHeight="1" s="1"/>
+    <row r="203" ht="78" customHeight="1" s="1"/>
+    <row r="204" ht="78" customHeight="1" s="1"/>
+    <row r="205" ht="78" customHeight="1" s="1"/>
+    <row r="206" ht="78" customHeight="1" s="1"/>
+    <row r="207" ht="78" customHeight="1" s="1"/>
+    <row r="208" ht="78" customHeight="1" s="1"/>
+    <row r="209" ht="78" customHeight="1" s="1"/>
+    <row r="210" ht="78" customHeight="1" s="1"/>
+    <row r="211" ht="78" customHeight="1" s="1"/>
+    <row r="212" ht="78" customHeight="1" s="1"/>
+    <row r="213" ht="78" customHeight="1" s="1"/>
+    <row r="214" ht="78" customHeight="1" s="1"/>
+    <row r="215" ht="78" customHeight="1" s="1"/>
+    <row r="216" ht="78" customHeight="1" s="1"/>
+    <row r="217" ht="78" customHeight="1" s="1"/>
+    <row r="218" ht="78" customHeight="1" s="1"/>
+    <row r="219" ht="78" customHeight="1" s="1"/>
+    <row r="220" ht="78" customHeight="1" s="1"/>
+    <row r="221" ht="78" customHeight="1" s="1"/>
+    <row r="222" ht="78" customHeight="1" s="1"/>
+    <row r="223" ht="78" customHeight="1" s="1"/>
+    <row r="224" ht="78" customHeight="1" s="1"/>
+    <row r="225" ht="78" customHeight="1" s="1"/>
+    <row r="226" ht="78" customHeight="1" s="1"/>
+    <row r="227" ht="78" customHeight="1" s="1"/>
+    <row r="228" ht="78" customHeight="1" s="1"/>
+    <row r="229" ht="78" customHeight="1" s="1"/>
+    <row r="230" ht="78" customHeight="1" s="1"/>
+    <row r="231" ht="78" customHeight="1" s="1"/>
+    <row r="232" ht="78" customHeight="1" s="1"/>
+    <row r="233" ht="78" customHeight="1" s="1"/>
+    <row r="234" ht="78" customHeight="1" s="1"/>
+    <row r="235" ht="78" customHeight="1" s="1"/>
+    <row r="236" ht="78" customHeight="1" s="1"/>
+    <row r="237" ht="78" customHeight="1" s="1"/>
+    <row r="238" ht="78" customHeight="1" s="1"/>
+    <row r="239" ht="78" customHeight="1" s="1"/>
+    <row r="240" ht="78" customHeight="1" s="1"/>
+    <row r="241" ht="78" customHeight="1" s="1"/>
+    <row r="242" ht="78" customHeight="1" s="1"/>
+    <row r="243" ht="78" customHeight="1" s="1"/>
+    <row r="244" ht="78" customHeight="1" s="1"/>
+    <row r="245" ht="78" customHeight="1" s="1"/>
+    <row r="246" ht="78" customHeight="1" s="1"/>
+    <row r="247" ht="78" customHeight="1" s="1"/>
+    <row r="248" ht="78" customHeight="1" s="1"/>
+    <row r="249" ht="78" customHeight="1" s="1"/>
+    <row r="250" ht="78" customHeight="1" s="1"/>
+    <row r="251" ht="78" customHeight="1" s="1"/>
+    <row r="252" ht="78" customHeight="1" s="1"/>
+    <row r="253" ht="78" customHeight="1" s="1"/>
+    <row r="254" ht="78" customHeight="1" s="1"/>
+    <row r="255" ht="78" customHeight="1" s="1"/>
+    <row r="256" ht="78" customHeight="1" s="1"/>
+    <row r="257" ht="78" customHeight="1" s="1"/>
+    <row r="258" ht="78" customHeight="1" s="1"/>
+    <row r="259" ht="78" customHeight="1" s="1"/>
+    <row r="260" ht="78" customHeight="1" s="1"/>
+    <row r="261" ht="78" customHeight="1" s="1"/>
+    <row r="262" ht="78" customHeight="1" s="1"/>
+    <row r="263" ht="78" customHeight="1" s="1"/>
+    <row r="264" ht="78" customHeight="1" s="1"/>
+    <row r="265" ht="78" customHeight="1" s="1"/>
+    <row r="266" ht="78" customHeight="1" s="1"/>
+    <row r="267" ht="78" customHeight="1" s="1"/>
+    <row r="268" ht="78" customHeight="1" s="1"/>
+    <row r="269" ht="78" customHeight="1" s="1"/>
+    <row r="270" ht="78" customHeight="1" s="1"/>
+    <row r="271" ht="78" customHeight="1" s="1"/>
+    <row r="272" ht="78" customHeight="1" s="1"/>
+    <row r="273" ht="78" customHeight="1" s="1"/>
+    <row r="274" ht="78" customHeight="1" s="1"/>
+    <row r="275" ht="78" customHeight="1" s="1"/>
+    <row r="276" ht="78" customHeight="1" s="1"/>
+    <row r="277" ht="78" customHeight="1" s="1"/>
+    <row r="278" ht="78" customHeight="1" s="1"/>
+    <row r="279" ht="78" customHeight="1" s="1"/>
+    <row r="280" ht="78" customHeight="1" s="1"/>
+    <row r="281" ht="78" customHeight="1" s="1"/>
+    <row r="282" ht="78" customHeight="1" s="1"/>
+    <row r="283" ht="78" customHeight="1" s="1"/>
+    <row r="284" ht="78" customHeight="1" s="1"/>
+    <row r="285" ht="78" customHeight="1" s="1"/>
+    <row r="286" ht="78" customHeight="1" s="1"/>
+    <row r="287" ht="78" customHeight="1" s="1"/>
+    <row r="288" ht="78" customHeight="1" s="1"/>
+    <row r="289" ht="78" customHeight="1" s="1"/>
+    <row r="290" ht="78" customHeight="1" s="1"/>
+    <row r="291" ht="78" customHeight="1" s="1"/>
+    <row r="292" ht="78" customHeight="1" s="1"/>
+    <row r="293" ht="78" customHeight="1" s="1"/>
+    <row r="294" ht="78" customHeight="1" s="1"/>
+    <row r="295" ht="78" customHeight="1" s="1"/>
+    <row r="296" ht="78" customHeight="1" s="1"/>
+    <row r="297" ht="78" customHeight="1" s="1"/>
+    <row r="298" ht="78" customHeight="1" s="1"/>
+    <row r="299" ht="78" customHeight="1" s="1"/>
+    <row r="300" ht="78" customHeight="1" s="1"/>
+    <row r="301" ht="78" customHeight="1" s="1"/>
+    <row r="302" ht="78" customHeight="1" s="1"/>
+    <row r="303" ht="78" customHeight="1" s="1"/>
+    <row r="304" ht="78" customHeight="1" s="1"/>
+    <row r="305" ht="78" customHeight="1" s="1"/>
+    <row r="306" ht="78" customHeight="1" s="1"/>
+    <row r="307" ht="78" customHeight="1" s="1"/>
+    <row r="308" ht="78" customHeight="1" s="1"/>
+    <row r="309" ht="78" customHeight="1" s="1"/>
+    <row r="310" ht="78" customHeight="1" s="1"/>
+    <row r="311" ht="78" customHeight="1" s="1"/>
+    <row r="312" ht="78" customHeight="1" s="1"/>
+    <row r="313" ht="78" customHeight="1" s="1"/>
+    <row r="314" ht="78" customHeight="1" s="1"/>
+    <row r="315" ht="78" customHeight="1" s="1"/>
+    <row r="316" ht="78" customHeight="1" s="1"/>
+    <row r="317" ht="78" customHeight="1" s="1"/>
+    <row r="318" ht="78" customHeight="1" s="1"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:O4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/assets/report-template.xlsx
+++ b/assets/report-template.xlsx
@@ -1452,7 +1452,7 @@
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>EchoTik详情链接</t>
+          <t>商品详情链接</t>
         </is>
       </c>
       <c r="O1" s="2" t="inlineStr">
